--- a/artfynd/A 60668-2023 artfynd.xlsx
+++ b/artfynd/A 60668-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116483913</v>
+        <v>116484043</v>
       </c>
       <c r="B2" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Sävtjärnen (Lilla Sävtjärnen), Vrm</t>
+          <t>Lilla Sävtjärnen, Lilla Sävtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344026</v>
+        <v>344073</v>
       </c>
       <c r="R2" t="n">
-        <v>6604294</v>
+        <v>6604319</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Nyare och äldre hackmärken</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116484043</v>
+        <v>116483913</v>
       </c>
       <c r="B3" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Sävtjärnen (Lilla Sävtjärnen), Vrm</t>
+          <t>Lilla Sävtjärnen, Lilla Sävtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344073</v>
+        <v>344026</v>
       </c>
       <c r="R3" t="n">
-        <v>6604319</v>
+        <v>6604294</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nyare och äldre hackmärken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,12 +897,7 @@
         <v>116482429</v>
       </c>
       <c r="B4" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +930,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svenskmyrarna (Svenskmyrarna), Vrm</t>
+          <t>Svenskmyrarna, Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1023,6 +1008,219 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116482603</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svenskmyrarna, Svenskmyrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>343998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6604371</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>59529638</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Holmesmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>343771</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6604282</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-03-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>JÄMNA-TJADERSPILL-BALGROPAR-MÅRDSPILL</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
